--- a/excel-files/TAGUIG_PATEROS/KAPITAN EDDIE T. REYES MEMORIAL INTEGRATED SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/KAPITAN EDDIE T. REYES MEMORIAL INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="598" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A7DAA1-2072-485A-9553-C60F8F8ABAD4}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F53E42F-F5A5-4972-8152-7C62DFEC6A01}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -2262,6 +2262,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2274,7 +2275,6 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6142,11 +6142,11 @@
     <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
-      <c r="C52" s="47">
+      <c r="C52" s="43">
         <f>C4+C10+C16+C23+C33+C43</f>
         <v>6312</v>
       </c>
-      <c r="D52" s="47">
+      <c r="D52" s="43">
         <f>SUM(D4:D51)</f>
         <v>10524</v>
       </c>
@@ -7322,8 +7322,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16:E21 E23:E31 E33:E41 E63:E71 E53:E61 E43:E51 E9:E14 E73:E81 E83:E91 E2:E7 E93:E102" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E93:E97 E83:E91 E73:E81 E63:E71 E53:E61 E43:E51 E33:E41 E23:E30 E16:E21 E9:E14 E2:E7 E98:E102 E31" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16:F21 F9:F14 F23:F31 F43:F51 F63:F71 F53:F61 F73:F81 F83:F91 F2:F7 F93:F102 F33:F41" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -7339,7 +7339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AB157"/>
+  <dimension ref="A1:AB127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -7369,38 +7369,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="45" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="46" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -15655,186 +15655,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -15862,8 +15682,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F43:F51 F33:F41 F23:F31 F63:F71 F14:F21 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 F73:F81" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -15882,7 +15702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB173"/>
+  <dimension ref="A1:AB143"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -15912,38 +15732,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="45" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="46" t="s">
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -24752,186 +24572,6 @@
       <c r="AA143" s="7"/>
       <c r="AB143" s="7"/>
     </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="171" spans="10:10">
-      <c r="J171" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="172" spans="10:10">
-      <c r="J172" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="173" spans="10:10">
-      <c r="J173" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C66 C68:C78 C80:C90 C92:C103 C105:C116" name="Textbooks"/>
@@ -24957,8 +24597,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S118:S125 Y118:Y125 G118:G125 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 Y55:Y66 S55:S66 M55:M66 M118:M125 M68:M78 G68:G78 Y68:Y78 S68:S78 S80:S90 M80:M90 G80:G90 Y80:Y90 G55:G66 Y92:Y103 G92:G103 M92:M103 S92:S103 M105:M116 S105:S116 Y105:Y116 G105:G116" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X68:X78 X80:X90 L55:L66 X92:X103 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L68:L78 L80:L90 R55:R66 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R68:R78 R80:R90 F55:F66 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F68:F78 F80:F90 F3:F10 X55:X66 X118:X125 F12:F19 F118:F125 R118:R125 L118:L125 L105:L116 R92:R103 X105:X116 L92:L103 F92:F103 R105:R116 F105:F116" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F118:F125 F105:F116 F92:F103 F80:F90 F68:F78 F55:F66 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L118:L125 L105:L116 L92:L103 L80:L90 L68:L78 L55:L66 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R118:R125 R105:R116 R92:R103 R80:R90 R68:R78 R55:R66 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X118:X125 X105:X116 X92:X103 X80:X90 X68:X78 X55:X66 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
